--- a/Team-Data/2008-09/2-23-2008-09.xlsx
+++ b/Team-Data/2008-09/2-23-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
         <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0.571</v>
+        <v>0.582</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -679,13 +746,13 @@
         <v>35.9</v>
       </c>
       <c r="J2" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
       <c r="K2" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L2" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M2" t="n">
         <v>20.7</v>
@@ -694,28 +761,28 @@
         <v>0.37</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P2" t="n">
         <v>26</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.732</v>
+        <v>0.735</v>
       </c>
       <c r="R2" t="n">
         <v>10.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V2" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W2" t="n">
         <v>7.6</v>
@@ -733,19 +800,19 @@
         <v>20.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE2" t="n">
         <v>11</v>
       </c>
-      <c r="AE2" t="n">
-        <v>12</v>
-      </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -766,13 +833,13 @@
         <v>8</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
         <v>14</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
@@ -784,25 +851,25 @@
         <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -811,7 +878,7 @@
         <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -858,73 +925,73 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.392</v>
+        <v>0.384</v>
       </c>
       <c r="O3" t="n">
         <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.776</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.9</v>
+        <v>101.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -945,28 +1012,28 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -975,22 +1042,22 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1136,7 +1203,7 @@
         <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP4" t="n">
         <v>20</v>
@@ -1154,7 +1221,7 @@
         <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
@@ -1169,10 +1236,10 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>0.436</v>
+        <v>0.446</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1225,46 +1292,46 @@
         <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
         <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O5" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.7</v>
@@ -1273,28 +1340,28 @@
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AD5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF5" t="n">
         <v>17</v>
       </c>
-      <c r="AE5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>18</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
         <v>22</v>
@@ -1315,13 +1382,13 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO5" t="n">
         <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1354,7 +1421,7 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -1389,49 +1456,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" t="n">
         <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J6" t="n">
-        <v>78.5</v>
+        <v>78.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.388</v>
+        <v>0.386</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0.752</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
         <v>31.1</v>
@@ -1440,10 +1507,10 @@
         <v>41.8</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
@@ -1455,25 +1522,25 @@
         <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
@@ -1485,25 +1552,25 @@
         <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
         <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>23</v>
@@ -1521,25 +1588,25 @@
         <v>24</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1719,7 @@
         <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,7 +1728,7 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
@@ -1691,13 +1758,13 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
         <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
         <v>9</v>
@@ -1721,7 +1788,7 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>0.649</v>
+        <v>0.661</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="J8" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.47</v>
+        <v>0.472</v>
       </c>
       <c r="L8" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M8" t="n">
         <v>17.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.364</v>
+        <v>0.369</v>
       </c>
       <c r="O8" t="n">
         <v>23.1</v>
@@ -1792,7 +1859,7 @@
         <v>30.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="R8" t="n">
         <v>10.4</v>
@@ -1804,13 +1871,13 @@
         <v>40.9</v>
       </c>
       <c r="U8" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V8" t="n">
         <v>15.9</v>
       </c>
       <c r="W8" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="X8" t="n">
         <v>5.7</v>
@@ -1825,19 +1892,19 @@
         <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.2</v>
+        <v>103.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
         <v>6</v>
@@ -1846,22 +1913,22 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1876,7 +1943,7 @@
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT8" t="n">
         <v>17</v>
@@ -1885,7 +1952,7 @@
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,7 +1964,7 @@
         <v>27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -1906,7 +1973,7 @@
         <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-1</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2049,10 +2116,10 @@
         <v>29</v>
       </c>
       <c r="AP9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR9" t="n">
         <v>16</v>
@@ -2061,7 +2128,7 @@
         <v>16</v>
       </c>
       <c r="AT9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU9" t="n">
         <v>23</v>
@@ -2073,13 +2140,13 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
         <v>6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.351</v>
+        <v>0.357</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
@@ -2135,10 +2202,10 @@
         <v>39.3</v>
       </c>
       <c r="J10" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L10" t="n">
         <v>6.6</v>
@@ -2147,31 +2214,31 @@
         <v>17.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O10" t="n">
         <v>22.9</v>
       </c>
       <c r="P10" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R10" t="n">
         <v>11.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T10" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U10" t="n">
         <v>20.8</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W10" t="n">
         <v>8.1</v>
@@ -2186,22 +2253,22 @@
         <v>22.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.1</v>
+        <v>108.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
@@ -2246,13 +2313,13 @@
         <v>12</v>
       </c>
       <c r="AU10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV10" t="n">
         <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2389,16 +2456,16 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
         <v>26</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>5</v>
@@ -2413,7 +2480,7 @@
         <v>11</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
@@ -2422,7 +2489,7 @@
         <v>17</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
         <v>4</v>
@@ -2431,25 +2498,25 @@
         <v>19</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" t="n">
         <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>0.407</v>
+        <v>0.414</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J12" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K12" t="n">
         <v>0.451</v>
@@ -2508,34 +2575,34 @@
         <v>7.8</v>
       </c>
       <c r="M12" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O12" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P12" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W12" t="n">
         <v>6.9</v>
@@ -2547,25 +2614,25 @@
         <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.8</v>
+        <v>104.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
         <v>21</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
         <v>6</v>
@@ -2592,7 +2659,7 @@
         <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AP12" t="n">
         <v>21</v>
@@ -2604,7 +2671,7 @@
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
@@ -2625,16 +2692,16 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -2663,70 +2730,70 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.246</v>
+        <v>0.232</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="J13" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.434</v>
       </c>
       <c r="L13" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M13" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.345</v>
       </c>
       <c r="O13" t="n">
         <v>17.1</v>
       </c>
       <c r="P13" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="R13" t="n">
         <v>11.3</v>
       </c>
       <c r="S13" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T13" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U13" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X13" t="n">
         <v>6.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z13" t="n">
         <v>20.9</v>
@@ -2735,13 +2802,13 @@
         <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.5</v>
+        <v>-8.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2753,7 +2820,7 @@
         <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2765,13 +2832,13 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
         <v>27</v>
@@ -2786,25 +2853,25 @@
         <v>11</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
@@ -2872,31 +2939,31 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P14" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R14" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
         <v>13.6</v>
@@ -2914,16 +2981,16 @@
         <v>20.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>109.2</v>
+        <v>108.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2989,7 +3056,7 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -3305,10 +3372,10 @@
         <v>18</v>
       </c>
       <c r="AJ16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3323,7 +3390,7 @@
         <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ16" t="n">
         <v>25</v>
@@ -3332,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT16" t="n">
         <v>28</v>
@@ -3344,10 +3411,10 @@
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
         <v>5</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
         <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>0.483</v>
+        <v>0.475</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,7 +3476,7 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K17" t="n">
         <v>0.45</v>
@@ -3418,34 +3485,34 @@
         <v>5.9</v>
       </c>
       <c r="M17" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="P17" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
         <v>12.2</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
         <v>7.2</v>
@@ -3457,19 +3524,19 @@
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
         <v>23.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>15</v>
@@ -3502,7 +3569,7 @@
         <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP17" t="n">
         <v>7</v>
@@ -3523,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>15</v>
@@ -3532,10 +3599,10 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3724,7 @@
         <v>25</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG18" t="n">
         <v>25</v>
@@ -3666,7 +3733,7 @@
         <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>5</v>
@@ -3681,10 +3748,10 @@
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP18" t="n">
         <v>14</v>
@@ -3696,7 +3763,7 @@
         <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT18" t="n">
         <v>11</v>
@@ -3720,10 +3787,10 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>0.439</v>
+        <v>0.429</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3773,19 +3840,19 @@
         <v>35.5</v>
       </c>
       <c r="J19" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M19" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.379</v>
+        <v>0.376</v>
       </c>
       <c r="O19" t="n">
         <v>19.2</v>
@@ -3794,16 +3861,16 @@
         <v>24.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R19" t="n">
         <v>11.1</v>
       </c>
       <c r="S19" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T19" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U19" t="n">
         <v>19.4</v>
@@ -3821,34 +3888,34 @@
         <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB19" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
       </c>
       <c r="AI19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
         <v>15</v>
@@ -3863,22 +3930,22 @@
         <v>7</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR19" t="n">
         <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
         <v>21</v>
@@ -3899,10 +3966,10 @@
         <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB19" t="n">
         <v>20</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6</v>
+        <v>0.593</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J20" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.456</v>
@@ -3967,31 +4034,31 @@
         <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="O20" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S20" t="n">
         <v>29.4</v>
       </c>
       <c r="T20" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="U20" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W20" t="n">
         <v>7.5</v>
@@ -4000,7 +4067,7 @@
         <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z20" t="n">
         <v>20.9</v>
@@ -4009,22 +4076,22 @@
         <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.3</v>
+        <v>96</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF20" t="n">
         <v>9</v>
       </c>
       <c r="AG20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4045,10 +4112,10 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
@@ -4060,13 +4127,13 @@
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
         <v>29</v>
       </c>
       <c r="AU20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
@@ -4087,7 +4154,7 @@
         <v>15</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
         <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.429</v>
+        <v>0.418</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J21" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.445</v>
@@ -4149,28 +4216,28 @@
         <v>28.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O21" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="P21" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.793</v>
+        <v>0.797</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
         <v>31.8</v>
       </c>
       <c r="T21" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="U21" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V21" t="n">
         <v>14.7</v>
@@ -4188,19 +4255,19 @@
         <v>20.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.8</v>
+        <v>105.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
         <v>19</v>
@@ -4209,7 +4276,7 @@
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4230,16 +4297,16 @@
         <v>20</v>
       </c>
       <c r="AO21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AQ21" t="n">
         <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
         <v>7</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ21" t="n">
         <v>6</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -4379,43 +4446,43 @@
         <v>-6.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF22" t="n">
         <v>27</v>
       </c>
       <c r="AG22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM22" t="n">
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>11</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -4621,13 +4688,13 @@
         <v>18</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24" t="n">
         <v>27</v>
       </c>
       <c r="F24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>0.491</v>
+        <v>0.5</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4683,16 +4750,16 @@
         <v>36.5</v>
       </c>
       <c r="J24" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L24" t="n">
         <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="N24" t="n">
         <v>0.315</v>
@@ -4701,10 +4768,10 @@
         <v>19.1</v>
       </c>
       <c r="P24" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="R24" t="n">
         <v>12.9</v>
@@ -4728,13 +4795,13 @@
         <v>5.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
         <v>20.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB24" t="n">
         <v>96.2</v>
@@ -4743,31 +4810,31 @@
         <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AE24" t="n">
         <v>16</v>
       </c>
       <c r="AF24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
         <v>17</v>
       </c>
       <c r="AJ24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK24" t="n">
         <v>16</v>
       </c>
       <c r="AL24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM24" t="n">
         <v>29</v>
@@ -4776,13 +4843,13 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
@@ -4797,10 +4864,10 @@
         <v>18</v>
       </c>
       <c r="AV24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
         <v>8</v>
@@ -4809,13 +4876,13 @@
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4998,7 @@
         <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG25" t="n">
         <v>13</v>
@@ -4949,13 +5016,13 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM25" t="n">
         <v>19</v>
       </c>
-      <c r="AM25" t="n">
-        <v>20</v>
-      </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
@@ -4985,7 +5052,7 @@
         <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -4994,7 +5061,7 @@
         <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB25" t="n">
         <v>3</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E26" t="n">
         <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.648</v>
+        <v>0.636</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L26" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N26" t="n">
         <v>0.382</v>
       </c>
       <c r="O26" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
         <v>13.2</v>
@@ -5077,7 +5144,7 @@
         <v>28.2</v>
       </c>
       <c r="T26" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U26" t="n">
         <v>20.8</v>
@@ -5092,43 +5159,43 @@
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.7</v>
+        <v>99.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5137,13 +5204,13 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
         <v>18</v>
@@ -5158,13 +5225,13 @@
         <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
         <v>14</v>
@@ -5176,10 +5243,10 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>0.207</v>
+        <v>0.211</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
@@ -5229,28 +5296,28 @@
         <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K27" t="n">
         <v>0.446</v>
       </c>
       <c r="L27" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M27" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O27" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="P27" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.803</v>
+        <v>0.805</v>
       </c>
       <c r="R27" t="n">
         <v>10</v>
@@ -5259,7 +5326,7 @@
         <v>28.5</v>
       </c>
       <c r="T27" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="U27" t="n">
         <v>19.9</v>
@@ -5271,25 +5338,25 @@
         <v>6.9</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
         <v>5.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.5</v>
+        <v>-9.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5310,22 +5377,22 @@
         <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
         <v>15</v>
       </c>
       <c r="AM27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN27" t="n">
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
@@ -5346,13 +5413,13 @@
         <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5486,16 +5553,16 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
@@ -5516,7 +5583,7 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
         <v>20</v>
@@ -5534,7 +5601,7 @@
         <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -5686,10 +5753,10 @@
         <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,7 +5765,7 @@
         <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
         <v>27</v>
@@ -5707,7 +5774,7 @@
         <v>11</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.596</v>
+        <v>0.589</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J30" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -5787,28 +5854,28 @@
         <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="O30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P30" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R30" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
         <v>29.2</v>
       </c>
       <c r="T30" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U30" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V30" t="n">
         <v>14.9</v>
@@ -5823,19 +5890,19 @@
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA30" t="n">
         <v>23.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>102.7</v>
+        <v>102.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>9</v>
@@ -5847,13 +5914,13 @@
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI30" t="n">
         <v>7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK30" t="n">
         <v>4</v>
@@ -5883,7 +5950,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5895,13 +5962,13 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
         <v>15</v>
       </c>
       <c r="AZ30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA30" t="n">
         <v>1</v>
@@ -5910,7 +5977,7 @@
         <v>7</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
@@ -6017,19 +6084,19 @@
         <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF31" t="n">
         <v>27</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI31" t="n">
         <v>19</v>
@@ -6053,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>20</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-23-2008-09</t>
+          <t>2009-02-23</t>
         </is>
       </c>
     </row>
